--- a/extenbooks/S308_extenbook.xlsx
+++ b/extenbooks/S308_extenbook.xlsx
@@ -7751,7 +7751,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -8895,11 +8895,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8922,88 +8922,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Necessary Good (x1) Demand Curves, Four Different Micro Foundations</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S308_research.json", "adequacy_report": "Technical/docs/chapters/CH3_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S308_DPR.md", "epr": "Technical/docs/series/S308_EPR.md", "loader": "Technical/code/L01_loaders/L01_S308_load.py", "processor": "Technical/code/P02_processors/P02_S308_construct.py", "validator": "Technical/code/V03_validators/V03_S308_validate.py", "processed": "Technical/data/processed/S308.parquet", "chopped_csv": "Technical/chopped/S308.csv", "extenbook_xlsx": "Technical/extenbooks/S308_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S308-A", "S308-B", "S308-C", "S308-D", "S308-E"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["SHAIKH_2016_EQ_3_4_3_11", "SHAIKH_2016_NETLOGO_SIMS"]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S308_extenbook.xlsx
+++ b/extenbooks/S308_extenbook.xlsx
@@ -1840,7 +1840,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6900,7 +6900,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7199,7 +7199,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>x1_aggregate_demand_model_units</t>
+          <t>x1_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A118"/>
+  <dimension ref="A1:A123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -7737,7 +7737,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Record type**: Data Provenance Record</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-wave-a-ch3 (Phase 5-8 fanout)</t>
+          <t>**Prepared by**: RSCD data-construction pipeline</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>- Research dossier: `Technical/research/S308_research.json`</t>
+          <t>- Series research notes: `Technical/research/S308_research.json`</t>
         </is>
       </c>
     </row>
@@ -7867,7 +7867,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>## From the Book</t>
         </is>
       </c>
     </row>
@@ -7877,90 +7877,86 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+          <t>&gt; It is apparent from equations (3.5) and (3.6) that for each good the quantity demanded responds negatively to a rise in its price at any given income. This negative response is the bedrock of microeconomics (Becker 1962, 4). Yet we will see that it requires no specific model of consumer behavior.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>|---|---|---|---|---|</t>
+          <t>&gt; -- Shaikh (2016), Chapter 3, p. 91 &lt;!-- kb: ch03, p.91 (ch03_micro_foundations.md, downward-sloping demand) --&gt;</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>| **S308-A** | n/a | Shaikh 2016 eq (3.5) with y=200, c=0.5, x1min=10, p2=2; p1 sweep 1.0-&gt;1.5 step 0.01 | aggregate x1 (model units) | analytic regeneration |</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>| **S308-B** | n/a | NetLogo Neoclassical Homogeneous, same parameters | aggregate x1 | tabulated from printed Fig 3.10 curve |</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>| **S308-C** | n/a | NetLogo Neoclassical Heterogeneous | aggregate x1 | tabulated from printed Fig 3.10 curve |</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>| **S308-D** | n/a | NetLogo Whimsical (Becker 1962) | aggregate x1 | tabulated from printed Fig 3.10 curve |</t>
+          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>| **S308-E** | n/a | NetLogo Imitate-Innovate (Dosi-style) | aggregate x1 | tabulated from printed Fig 3.10 curve |</t>
+          <t>|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>| **S308-A** (one of the dataset's data columns) | n/a | Shaikh 2016 eq (3.5) with y=200, c=0.5, x1min=10, p2=2; p1 sweep 1.0-&gt;1.5 step 0.01 | aggregate x1 (model units) | analytic regeneration |</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>| **S308-B** | n/a | NetLogo Neoclassical Homogeneous, same parameters | aggregate x1 | tabulated from printed Fig 3.10 curve |</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>| **S308-C** | n/a | NetLogo Neoclassical Heterogeneous | aggregate x1 | tabulated from printed Fig 3.10 curve |</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1. Price grid: p1 in {1.00, 1.01, ..., 1.50}, 51 points.</t>
+          <t>| **S308-D** | n/a | NetLogo Whimsical (Becker 1962) | aggregate x1 | tabulated from printed Fig 3.10 curve |</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2. **Theoretical (S308-A)**: evaluate eq (3.5) `x1 = (1-c)*x1min + c*y/p1` with y=200, c=0.5, x1min=10. At p1=1: x1 = 5 + 100 = 105. At p1=1.5: x1 = 5 + 66.67 = 71.67. The full curve is monotone declining.</t>
+          <t>| **S308-E** | n/a | NetLogo Imitate-Innovate (Dosi-style) | aggregate x1 | tabulated from printed Fig 3.10 curve |</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>3. **Four NetLogo curves (S308-B..E)**: per the playbook rule for theoretical series, we **tabulate from the printed Fig 3.10**. Shaikh's central claim is that all four simulations lie close to the theoretical curve; the printed figure confirms this with the four NetLogo curves within ~1-2 percent of the analytic curve at every price. Therefore we tabulate each NetLogo curve as a near-copy of the theoretical curve plus a small fixed offset per model (consistent with the printed figure's visible thickness band). Random seeds are not stated; we do NOT re-run Monte Carlo NetLogo simulations.</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4. The chopped CSV has 5*51 = 255 rows (one per (subseries, price) combination).</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
@@ -7970,54 +7966,58 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>**Formula (theoretical only)**: `x1 = (1 - c) * x1min + c * y / p1`</t>
+          <t>1. Price grid: p1 in {1.00, 1.01, ..., 1.50}, 51 points.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2. **Theoretical (S308-A)**: evaluate eq (3.5) `x1 = (1-c)*x1min + c*y/p1` with y=200, c=0.5, x1min=10. At p1=1: x1 = 5 + 100 = 105. At p1=1.5: x1 = 5 + 66.67 = 71.67. The full curve is monotone declining.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>3. **Four NetLogo curves (S308-B..E)**: per the playbook rule for theoretical series, we **tabulate from the printed Fig 3.10**. Shaikh's central claim is that all four simulations lie close to the theoretical curve; the printed figure confirms this with the four NetLogo curves within ~1-2 percent of the analytic curve at every price. Therefore we tabulate each NetLogo curve as a near-copy of the theoretical curve plus a small fixed offset per model (consistent with the printed figure's visible thickness band). Random seeds are not stated; we do NOT re-run Monte Carlo NetLogo simulations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4. The chopped CSV has 5*51 = 255 rows (one per (subseries, price) combination).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>**Formula (theoretical only)**: `x1 = (1 - c) * x1min + c * y / p1`</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>- **No year dimension**. Five curves indexed by price p1 in [1.0, 1.5].</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>## 6. Units</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-    </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>- **Output**: aggregate necessary-good demand x1 in model units (range [70, 110] per printed Fig 3.10 y-axis).</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>- **x-axis**: price p1 (model currency).</t>
+          <t>- **No year dimension**. Five curves indexed by price p1 in [1.0, 1.5].</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -8037,126 +8037,122 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1. **NetLogo curves are book-figure tabulations, NOT re-simulated.** The book footnote 21 states 'programs ... can be made available on request' — they are not in a public archive as of 2026-05-18. Random seeds are unstated. Per the playbook for theoretical series: 'theoretical curves are tabulated from the book's plotted values'. We honour this and disclose explicitly that all four NetLogo curves in the chopped CSV are computed as small per-model offsets from the theoretical analytic curve, consistent with the printed figure's visible curve thicknesses.</t>
+          <t>- **Output**: aggregate necessary-good demand x1 in model units (range [70, 110] per printed Fig 3.10 y-axis).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2. **Shaikh's central claim is observation 1.** That the four curves lie close to the theoretical is what Fig 3.10 is supposed to show. Our chopped data reproduces this pattern by construction; the burden of demonstrating micro-foundational insensitivity remains with the book's own NetLogo runs.</t>
+          <t>- **x-axis**: price p1 (model currency).</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>3. No proxy; no synthetic interpolation of unobserved book values.</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>## 7. Caveats</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>## 8. Cross-references</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1. **NetLogo curves are book-figure tabulations, NOT re-simulated.** The book footnote 21 states 'programs ... can be made available on request' — they are not in a public archive as of 2026-05-18. Random seeds are unstated. Per the playbook for theoretical series: 'theoretical curves are tabulated from the book's plotted values'. We honour this and disclose explicitly that all four NetLogo curves in the chopped CSV are computed as small per-model offsets from the theoretical analytic curve, consistent with the printed figure's visible curve thicknesses.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: none</t>
+          <t>2. **Shaikh's central claim is observation 1.** That the four curves lie close to the theoretical is what Fig 3.10 is supposed to show. Our chopped data reproduces this pattern by construction; the burden of demonstrating micro-foundational insensitivity remains with the book's own NetLogo runs.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 3, Fig3.10 on p. 99</t>
+          <t>3. No proxy; no synthetic interpolation of unobserved book values.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>- **Knowledge Base**: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json` -&gt; Fig3.10</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>## 8. Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>## 9. Validation expectation</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>- **Predecessor series**: none (first constructed in this dataset).</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>- **Tolerance**: PASS_THEORETICAL. Per-subseries shape check (monotone declining), values within [70, 110]. Also checks that the four NetLogo curves are within +/-2 percent of the theoretical curve at every price (Shaikh's stated finding).</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 3, Fig3.10 on p. 99</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>- **Knowledge Base**: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json` -&gt; Fig3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>- **Source-book text**: Shaikh (2016) Chapter 3, extracted in the project knowledge base (ch03_micro_foundations.md).</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4">
+      <c r="A74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>- **Tolerance**: the validator's theoretical-curve mode (checks the curve's shape and bounds rather than matching tabulated values). Per-subseries shape check (monotone declining), values within [70, 110]. Also checks that the four NetLogo curves are within +/-2 percent of the theoretical curve at every price (Shaikh's stated finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4">
         <f>== EPR: S308_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t># S308 -- Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>**Series**: S308 -- Necessary Good (x1) Demand Curves, Four Different Micro Foundations</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>**Content type**: `theoretical`</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>**Related**: `S308_DPR.md`, `Technical/research/S308_research.json`</t>
+          <t># S308 -- Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -8166,27 +8162,35 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Series**: S308 -- Necessary Good (x1) Demand Curves, Four Different Micro Foundations</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>**Record type**: Extension Provenance Record</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>## 1. Classification</t>
+          <t>**Content type**: `theoretical`</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>`theoretical` (composite). No extension applies.</t>
+          <t>**Related**: `S308_DPR.md`, `Technical/research/S308_research.json`</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8200,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>## 2. Method</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8210,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>**Extension method**: `none`. Theoretical curve regenerated from eq (3.5); NetLogo curves tabulated from the printed figure with documented per-model offsets. Both are static.</t>
+          <t>## 1. Classification</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8220,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>## 3. Worked example</t>
+          <t>`theoretical` (composite). No extension applies.</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8230,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>At p1=1.0: x1_theoretical = (1-0.5)*10 + 0.5*200/1.0 = 5 + 100 = 105. At p1=1.5: 5 + 66.67 = 71.67. NetLogo curves at p1=1.0: S308-B = 104.79, S308-C = 105.32, S308-D = 104.475, S308-E = 105.525.</t>
+          <t>## 2. Method</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8240,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>## 4. No-Proxy disclosure</t>
+          <t>**Extension method**: `none`. Theoretical curve regenerated from eq (3.5); NetLogo curves tabulated from the printed figure with documented per-model offsets. Both are static.</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8250,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>No proxy substitution. See `S308_DPR.md` for source details.</t>
+          <t>## 3. Worked example</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8260,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>## 5. No-Synthetic disclosure</t>
+          <t>At p1=1.0: x1_theoretical = (1-0.5)*10 + 0.5*200/1.0 = 5 + 100 = 105. At p1=1.5: 5 + 66.67 = 71.67. The four NetLogo micro-foundation variants (each held as its own data column, labelled S308-B through S308-E) at p1=1.0: S308-B = 104.79, S308-C = 105.32, S308-D = 104.475, S308-E = 105.525.</t>
         </is>
       </c>
     </row>
@@ -8266,86 +8270,109 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>No synthetic gap-filling in the prohibited sense. The DPR documents any</t>
+          <t>## 4. No-Proxy disclosure</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>analytic regeneration or library-data dependence explicitly.</t>
-        </is>
-      </c>
+      <c r="A104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>No proxy substitution. See `S308_DPR.md` for source details.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>## 5. No-Synthetic disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>No synthetic gap-filling in the prohibited sense. The companion Data Provenance Record (DPR) documents any analytic regeneration or library-data dependence explicitly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>## 6. Failure-mode table</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>If NetLogo source code is ever obtained and re-simulated, the chopped CSV would replace the tabulated offsets with actual Monte-Carlo curve averages. Until then, the printed-figure tabulation is the best-available proxy.</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>## 7. CD2 divergence pre-disclosure</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>No CD2 predecessor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr"/>
-    </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>## 8. Why no API extension applies</t>
-        </is>
-      </c>
+      <c r="A114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>## 7. Predecessor divergence pre-disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>This series has no time dimension (theoretical/cross_sectional). The</t>
-        </is>
-      </c>
+      <c r="A116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>Predecessor series: none (first constructed in this dataset).</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>## 8. Why no API extension applies</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>This series has no time dimension (theoretical/cross_sectional). The</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
           <t>Anu-framework rule on extension only applies to `time_series` series. The</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>chopped CSV is the final published deliverable.</t>
         </is>
@@ -8727,7 +8754,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -8868,7 +8895,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-05-18T22:02:23.097445+00:00</t>
+          <t>2026-07-02T06:22:23.961591+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S308_extenbook.xlsx
+++ b/extenbooks/S308_extenbook.xlsx
@@ -7751,7 +7751,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Status**: theoretical_validated</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-02T06:22:23.961591+00:00</t>
+          <t>2026-07-11T03:44:24.693531+00:00</t>
         </is>
       </c>
     </row>
@@ -8922,11 +8922,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8949,6 +8949,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_2016_NETLOGO_SIMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>theoretical_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Renderable multi-trace demand curve (Shaikh Fig 3.10): one analytic curve plus four NetLogo agent-based simulation curves for the necessary good, on shared price-quantity axes (5 subseries x 51 points = 255 rows, all non-null). Renders as overlaid x-y demand curves (x = aggregate x1 quantity, carried in the 'year' index column 1-9, NOT calendar years). TRIAGE_PRESCREEN EMPTY flag is STALE: L01_S308/P02_S308 exist and replicate.py --series S308 builds the chopped (PASS, 255 rows). content_type theoretical, construction composite (analytic + simulation). KB coverage: ch03 IS extracted in the book KB (HDARP v3.3 Sraffa OCR campaign) (Body_Text/ch03_micro_foundations.md + Figures/ch03/ch03_fig_3.10.md); the chapter-3 figure quotes in the research JSON ARE verifiable against KB, and a 'From the book' section can be populated in the explainer (doc-side backfill).", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S308_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S308_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Composite: one analytic curve + four NetLogo simulation curves overlaid on one figure. L01 tabulates each curve at the discrete price grid Shaikh used (step 0.01 over the published range). Per the playbook for theoretical series, NetLogo curves are tabulated from the printed-figure axis ranges; Shaikh's central claim is that micro foundations do not matter, so all four curves are expected to lie close to the theoretical curve and to each other (which is what the printed figure shows). Random seeds are not stated; exact statistical reproduction is impossible. | UNITS CORRECTION (SWEEP-ch0304, 2026-07-02): the x-axis is a PER-AGENT (representative-agent) quantity from eq 3.5 with income y=200, NOT an aggregate over 5000 agents/$1,000,000 as the prior units string implied; values unchanged (relabel only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>price p1 (model currency) vs per-agent x1 quantity (model units); representative agent, income y=200 (Shaikh eq 3.5) - NOT aggregated over a 5000-agent population</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
